--- a/grupos/5BEM - Estadisticos 20241.xlsx
+++ b/grupos/5BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Miguel Lopez Yadira</t>
+  </si>
+  <si>
     <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Miguel Lopez Yadira</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,40 +215,82 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>CRESCENCIO</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>TOLEDO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
     <t>GEOVANNI</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -775,25 +817,25 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -820,7 +862,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -829,7 +871,7 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>9</v>
@@ -864,25 +906,25 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -909,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -921,10 +963,10 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -953,25 +995,25 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -998,10 +1040,10 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1013,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1042,25 +1084,25 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1102,7 +1144,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1131,25 +1173,25 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1176,7 +1218,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1220,25 +1262,25 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1262,10 +1304,10 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1274,7 +1316,7 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1309,25 +1351,25 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1354,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1363,13 +1405,13 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1398,25 +1440,25 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1443,7 +1485,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1452,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1487,25 +1529,25 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1529,25 +1571,25 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1576,25 +1618,25 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1621,7 +1663,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1630,13 +1672,13 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1665,25 +1707,25 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1713,7 +1755,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1722,7 +1764,7 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -1754,25 +1796,25 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1796,10 +1838,10 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1808,7 +1850,7 @@
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>9</v>
@@ -1843,25 +1885,25 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1888,22 +1930,22 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1932,25 +1974,25 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1977,22 +2019,22 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB17">
         <v>5</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2021,25 +2063,25 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2063,22 +2105,22 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2110,25 +2152,25 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2155,7 +2197,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2167,7 +2209,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2199,25 +2241,25 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2241,10 +2283,10 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2253,7 +2295,7 @@
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>10</v>
@@ -2288,25 +2330,25 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2342,13 +2384,13 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2377,25 +2419,25 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2422,19 +2464,19 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2466,25 +2508,25 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2508,10 +2550,10 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2520,13 +2562,13 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2555,25 +2597,25 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2600,19 +2642,19 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>5</v>
@@ -2644,25 +2686,25 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2686,25 +2728,25 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2733,25 +2775,25 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2778,7 +2820,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2787,13 +2829,13 @@
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2822,25 +2864,25 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2864,10 +2906,10 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2879,10 +2921,10 @@
         <v>10</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2911,25 +2953,25 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2953,25 +2995,25 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3000,25 +3042,25 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3042,22 +3084,22 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3089,25 +3131,25 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3137,13 +3179,13 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>7</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3178,25 +3220,25 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3220,10 +3262,10 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3232,10 +3274,10 @@
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -3267,25 +3309,25 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3309,22 +3351,22 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3356,25 +3398,25 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3398,22 +3440,22 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z33">
         <v>6</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -3445,25 +3487,25 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3487,19 +3529,19 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>8</v>
@@ -3659,7 +3701,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -3680,7 +3722,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3792,10 +3834,10 @@
         <v>85</v>
       </c>
       <c r="I6">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J6">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3810,13 +3852,13 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P6">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q6">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3831,7 +3873,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3931,7 +3973,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3952,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -3996,10 +4038,10 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J9">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -4017,10 +4059,10 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q9">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4064,7 +4106,7 @@
         <v>75</v>
       </c>
       <c r="I10">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4082,10 +4124,10 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4103,7 +4145,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4132,7 +4174,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -4153,7 +4195,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4200,7 +4242,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4221,7 +4263,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4268,10 +4310,10 @@
         <v>80</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J13">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4286,13 +4328,13 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4307,7 +4349,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4336,10 +4378,10 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="J14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4357,10 +4399,10 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="Q14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4404,7 +4446,7 @@
         <v>85</v>
       </c>
       <c r="I15">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4422,10 +4464,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4443,7 +4485,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4475,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4496,7 +4538,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4540,10 +4582,10 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J17">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -4561,10 +4603,10 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q17">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4608,10 +4650,10 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4629,10 +4671,10 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q18">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4676,10 +4718,10 @@
         <v>85</v>
       </c>
       <c r="I19">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J19">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -4694,13 +4736,13 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q19">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4715,7 +4757,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4744,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4765,7 +4807,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4880,10 +4922,10 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4901,10 +4943,10 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4948,10 +4990,10 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -4969,10 +5011,10 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Q23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5016,10 +5058,10 @@
         <v>85</v>
       </c>
       <c r="I24">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -5034,13 +5076,13 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P24">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5055,7 +5097,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5087,7 +5129,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -5108,7 +5150,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -5152,7 +5194,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -5173,7 +5215,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5220,10 +5262,10 @@
         <v>85</v>
       </c>
       <c r="I27">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -5238,13 +5280,13 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P27">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q27">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5259,7 +5301,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5288,10 +5330,10 @@
         <v>80</v>
       </c>
       <c r="I28">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J28">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -5306,13 +5348,13 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q28">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5327,7 +5369,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5356,10 +5398,10 @@
         <v>85</v>
       </c>
       <c r="I29">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J29">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -5374,13 +5416,13 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P29">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q29">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5395,7 +5437,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5424,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5445,7 +5487,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5492,10 +5534,10 @@
         <v>80</v>
       </c>
       <c r="I31">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J31">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5510,13 +5552,13 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P31">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q31">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5531,7 +5573,7 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5563,7 +5605,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5584,7 +5626,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5646,7 +5688,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5667,7 +5709,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -5696,10 +5738,10 @@
         <v>85</v>
       </c>
       <c r="I34">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="J34">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -5714,13 +5756,13 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P34">
-        <v>95</v>
+        <v>97.3</v>
       </c>
       <c r="Q34">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5735,7 +5777,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
   </sheetData>
@@ -5824,7 +5866,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5833,19 +5875,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>64.5</v>
+        <v>93.5</v>
       </c>
       <c r="G3" s="2">
-        <v>35.5</v>
+        <v>6.5</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5856,7 +5898,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5865,19 +5907,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>77.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="G4" s="2">
-        <v>22.6</v>
+        <v>6.5</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5888,28 +5930,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>31</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>77.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="G5" s="2">
-        <v>22.6</v>
+        <v>6.5</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5920,28 +5962,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="G6" s="2">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5952,7 +5994,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5961,19 +6003,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5984,7 +6026,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -6005,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6055,7 +6097,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6087,16 +6129,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920033</v>
+        <v>22330051920189</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6110,19 +6152,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920033</v>
+        <v>22330051920189</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -6133,16 +6175,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920051</v>
+        <v>22330051920043</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6156,22 +6198,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920051</v>
+        <v>22330051920043</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6179,22 +6221,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920034</v>
+        <v>22330051920045</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6202,24 +6244,162 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920036</v>
+        <v>22330051920045</v>
       </c>
       <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920033</v>
+      </c>
+      <c r="B8" t="s">
         <v>68</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920038</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920327</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920048</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920049</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920051</v>
+      </c>
+      <c r="B13" t="s">
         <v>72</v>
       </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20241.xlsx
+++ b/grupos/5BEM - Estadisticos 20241.xlsx
@@ -188,7 +188,7 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
+    <t>Martínez Sota Luis Rey</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>

--- a/grupos/5BEM - Estadisticos 20241.xlsx
+++ b/grupos/5BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -215,6 +215,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>JENKINS</t>
   </si>
   <si>
@@ -224,19 +227,7 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>TOLEDO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>ACOSTA</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -245,25 +236,13 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>MIGUEL ANTONIO</t>
   </si>
   <si>
     <t>ARTHUR RICHARD</t>
@@ -272,25 +251,10 @@
     <t>AARON MIGUEL</t>
   </si>
   <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
     <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
   </si>
 </sst>
 </file>
@@ -826,7 +790,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -915,7 +879,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1004,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1093,7 +1057,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1135,7 +1099,7 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1182,7 +1146,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1224,7 +1188,7 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1271,7 +1235,7 @@
         <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1313,7 +1277,7 @@
         <v>8</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1360,7 +1324,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1449,7 +1413,7 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1538,7 +1502,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1627,7 +1591,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1669,7 +1633,7 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1716,7 +1680,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1758,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1805,7 +1769,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1847,7 +1811,7 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1894,7 +1858,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -1983,7 +1947,7 @@
         <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -2025,7 +1989,7 @@
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>6</v>
@@ -2072,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2114,7 +2078,7 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2161,7 +2125,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2250,7 +2214,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2339,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>8</v>
@@ -2428,7 +2392,7 @@
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2470,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>6</v>
@@ -2517,7 +2481,7 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2606,7 +2570,7 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -2648,7 +2612,7 @@
         <v>6</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -2695,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2784,7 +2748,7 @@
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2873,7 +2837,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2962,7 +2926,7 @@
         <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -3004,7 +2968,7 @@
         <v>6</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -3051,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -3093,7 +3057,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>9</v>
@@ -3140,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3229,7 +3193,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -3271,7 +3235,7 @@
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>6</v>
@@ -3318,7 +3282,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -3407,7 +3371,7 @@
         <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>8</v>
@@ -3496,7 +3460,7 @@
         <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>8</v>
@@ -3538,7 +3502,7 @@
         <v>8</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>7</v>
@@ -3843,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>82.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3864,7 +3828,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>82.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -3979,7 +3943,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4000,7 +3964,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4047,7 +4011,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4068,7 +4032,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>82.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4183,7 +4147,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -4204,7 +4168,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4523,7 +4487,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>87</v>
+        <v>90.7</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -4544,7 +4508,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>87</v>
+        <v>90.7</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4727,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -4748,7 +4712,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>78.3</v>
+        <v>86</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -5067,7 +5031,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -5088,7 +5052,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5135,7 +5099,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -5156,7 +5120,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -5543,7 +5507,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>87</v>
+        <v>90.7</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -5564,7 +5528,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>87</v>
+        <v>90.7</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -5747,7 +5711,7 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>87</v>
+        <v>90.7</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -5768,7 +5732,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>87</v>
+        <v>90.7</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -5843,19 +5807,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>64.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>35.5</v>
+        <v>12.9</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6097,7 +6061,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6129,16 +6093,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920189</v>
+        <v>22330051920038</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6155,13 +6119,13 @@
         <v>22330051920189</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6178,19 +6142,19 @@
         <v>22330051920043</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6198,22 +6162,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920043</v>
+        <v>22330051920327</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6224,182 +6188,21 @@
         <v>22330051920045</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920045</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920033</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920038</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920327</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920048</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920049</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920051</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20241.xlsx
+++ b/grupos/5BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -215,6 +215,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
@@ -227,6 +233,12 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>ACOSTA</t>
   </si>
   <si>
@@ -240,6 +252,12 @@
   </si>
   <si>
     <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
   </si>
   <si>
     <t>MIGUEL ANTONIO</t>
@@ -6061,7 +6079,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6093,16 +6111,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920038</v>
+        <v>22330051920031</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6116,19 +6134,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920189</v>
+        <v>22330051920031</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -6139,22 +6157,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920043</v>
+        <v>22330051920031</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6162,22 +6180,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920327</v>
+        <v>22330051920191</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
         <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6185,24 +6203,162 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
+        <v>22330051920191</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920191</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920038</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920189</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920043</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920327</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>22330051920045</v>
       </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
         <v>11</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F12" t="s">
         <v>58</v>
       </c>
-      <c r="G6">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20241.xlsx
+++ b/grupos/5BEM - Estadisticos 20241.xlsx
@@ -823,7 +823,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -912,7 +912,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1001,7 +1001,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1090,7 +1090,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1179,7 +1179,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1268,7 +1268,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1378,7 +1378,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1446,7 +1446,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1535,7 +1535,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1556,7 +1556,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1624,7 +1624,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1645,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1713,7 +1713,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1802,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1823,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1891,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1980,7 +1980,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2069,7 +2069,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2158,7 +2158,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2247,7 +2247,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2336,7 +2336,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2514,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2603,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2713,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2781,7 +2781,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2870,7 +2870,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2891,7 +2891,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2959,7 +2959,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3048,7 +3048,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3069,7 +3069,7 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -3137,7 +3137,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3226,7 +3226,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3247,7 +3247,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3315,7 +3315,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3404,7 +3404,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3493,7 +3493,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3704,7 +3704,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3840,7 +3840,7 @@
         <v>97.3</v>
       </c>
       <c r="Q6">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3976,7 +3976,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -4044,7 +4044,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="Q9">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4316,7 +4316,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4384,7 +4384,7 @@
         <v>97.3</v>
       </c>
       <c r="Q14">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4520,7 +4520,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4588,7 +4588,7 @@
         <v>97.3</v>
       </c>
       <c r="Q17">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4656,7 +4656,7 @@
         <v>97.3</v>
       </c>
       <c r="Q18">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4724,7 +4724,7 @@
         <v>97.3</v>
       </c>
       <c r="Q19">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4928,7 +4928,7 @@
         <v>97.3</v>
       </c>
       <c r="Q22">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4996,7 +4996,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="Q23">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5064,7 +5064,7 @@
         <v>97.3</v>
       </c>
       <c r="Q24">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5132,7 +5132,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -5268,7 +5268,7 @@
         <v>97.3</v>
       </c>
       <c r="Q27">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5336,7 +5336,7 @@
         <v>97.3</v>
       </c>
       <c r="Q28">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5404,7 +5404,7 @@
         <v>97.3</v>
       </c>
       <c r="Q29">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5540,7 +5540,7 @@
         <v>97.3</v>
       </c>
       <c r="Q31">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5608,7 +5608,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5676,7 +5676,7 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5744,7 +5744,7 @@
         <v>97.3</v>
       </c>
       <c r="Q34">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/5BEM - Estadisticos 20241.xlsx
+++ b/grupos/5BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Miguel Lopez Yadira</t>
+  </si>
+  <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Miguel Lopez Yadira</t>
-  </si>
-  <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,9 +227,6 @@
     <t>JENKINS</t>
   </si>
   <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -245,15 +242,9 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>RICARDO</t>
   </si>
   <si>
@@ -266,13 +257,7 @@
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
     <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
   </si>
 </sst>
 </file>
@@ -838,7 +823,7 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -927,7 +912,7 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -948,7 +933,7 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1016,7 +1001,7 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1105,7 +1090,7 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1194,7 +1179,7 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1283,7 +1268,7 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1372,7 +1357,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1461,7 +1446,7 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1482,7 +1467,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1550,7 +1535,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1639,7 +1624,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1728,7 +1713,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1817,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1906,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1995,7 +1980,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -2016,7 +2001,7 @@
         <v>5</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2084,7 +2069,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2173,7 +2158,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2194,7 +2179,7 @@
         <v>6</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2262,7 +2247,7 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2351,7 +2336,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2440,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2461,7 +2446,7 @@
         <v>6</v>
       </c>
       <c r="AC22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2529,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2550,7 +2535,7 @@
         <v>6</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2618,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2639,7 +2624,7 @@
         <v>6</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2707,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2796,7 +2781,7 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2885,7 +2870,7 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2974,7 +2959,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -3063,7 +3048,7 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3084,7 +3069,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3152,7 +3137,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3241,7 +3226,7 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3262,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3330,7 +3315,7 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3419,7 +3404,7 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3440,7 +3425,7 @@
         <v>9</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3508,7 +3493,7 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3855,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4059,7 +4044,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4127,7 +4112,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4331,7 +4316,7 @@
         <v>100</v>
       </c>
       <c r="V13">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4467,7 +4452,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4535,7 +4520,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4739,7 +4724,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5079,7 +5064,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5283,7 +5268,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5351,7 +5336,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5419,7 +5404,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5487,7 +5472,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5555,7 +5540,7 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5691,7 +5676,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -5759,7 +5744,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
     </row>
   </sheetData>
@@ -5912,28 +5897,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>31</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="G5" s="2">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5944,28 +5929,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5976,7 +5961,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5997,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6008,7 +5993,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>60</v>
@@ -6029,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6079,7 +6064,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6117,10 +6102,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6140,10 +6125,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6163,10 +6148,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -6186,10 +6171,10 @@
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6209,10 +6194,10 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6232,10 +6217,10 @@
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6255,10 +6240,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6278,10 +6263,10 @@
         <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6295,70 +6280,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920043</v>
+        <v>22330051920327</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920327</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920045</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20241.xlsx
+++ b/grupos/5BEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -215,46 +215,28 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>MELCHOR</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>ACOSTA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>RICARDO</t>
+    <t>MIGUEL ANTONIO</t>
   </si>
   <si>
     <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>JORGE IVAN</t>
@@ -805,22 +787,22 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -832,10 +814,10 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -894,22 +876,22 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -924,7 +906,7 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -983,22 +965,22 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1013,13 +995,13 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -1072,22 +1054,22 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1161,22 +1143,22 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1250,28 +1232,28 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1283,7 +1265,7 @@
         <v>7</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1339,22 +1321,22 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1372,7 +1354,7 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>7</v>
@@ -1428,22 +1410,22 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1517,22 +1499,22 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1544,10 +1526,10 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -1606,22 +1588,22 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1633,16 +1615,16 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1695,34 +1677,34 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1784,22 +1766,22 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1811,7 +1793,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <v>7</v>
@@ -1820,7 +1802,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -1873,22 +1855,22 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1900,7 +1882,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -1909,7 +1891,7 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>7</v>
@@ -1962,22 +1944,22 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1989,16 +1971,16 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2051,22 +2033,22 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2078,7 +2060,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <v>8</v>
@@ -2087,7 +2069,7 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2140,43 +2122,43 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>7</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2229,22 +2211,22 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2318,28 +2300,28 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2407,22 +2389,22 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2434,16 +2416,16 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>6</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2496,40 +2478,40 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>6</v>
@@ -2585,22 +2567,22 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2612,16 +2594,16 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2674,22 +2656,22 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2763,22 +2745,22 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2852,22 +2834,22 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2941,22 +2923,22 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2968,10 +2950,10 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>7</v>
@@ -3030,22 +3012,22 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -3119,22 +3101,22 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -3208,22 +3190,22 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -3241,10 +3223,10 @@
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC31">
         <v>6</v>
@@ -3297,28 +3279,28 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3333,7 +3315,7 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3386,22 +3368,22 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3416,7 +3398,7 @@
         <v>8</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3475,28 +3457,28 @@
         <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>8</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3505,10 +3487,10 @@
         <v>8</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB34">
         <v>8</v>
@@ -3822,7 +3804,7 @@
         <v>93.2</v>
       </c>
       <c r="P6">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q6">
         <v>95</v>
@@ -3831,7 +3813,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>86</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -3967,7 +3949,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4026,7 +4008,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>94.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="Q9">
         <v>98.8</v>
@@ -4035,7 +4017,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4094,7 +4076,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P10">
-        <v>94.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4103,7 +4085,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4162,7 +4144,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>94.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4171,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4230,7 +4212,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4298,7 +4280,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P13">
-        <v>94.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="Q13">
         <v>95</v>
@@ -4366,7 +4348,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q14">
         <v>97.5</v>
@@ -4434,7 +4416,7 @@
         <v>93.2</v>
       </c>
       <c r="P15">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4511,7 +4493,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4570,7 +4552,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q17">
         <v>97.5</v>
@@ -4638,7 +4620,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q18">
         <v>97.5</v>
@@ -4706,7 +4688,7 @@
         <v>93.2</v>
       </c>
       <c r="P19">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q19">
         <v>97.5</v>
@@ -4715,7 +4697,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>86</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -4774,7 +4756,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4910,7 +4892,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q22">
         <v>97.5</v>
@@ -4919,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -4978,7 +4960,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>94.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="Q23">
         <v>97.5</v>
@@ -4987,7 +4969,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5046,7 +5028,7 @@
         <v>93.2</v>
       </c>
       <c r="P24">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q24">
         <v>98.8</v>
@@ -5055,7 +5037,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5123,7 +5105,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -5182,7 +5164,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5250,7 +5232,7 @@
         <v>93.2</v>
       </c>
       <c r="P27">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q27">
         <v>98.8</v>
@@ -5259,7 +5241,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -5318,7 +5300,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P28">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q28">
         <v>97.5</v>
@@ -5386,7 +5368,7 @@
         <v>93.2</v>
       </c>
       <c r="P29">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q29">
         <v>98.8</v>
@@ -5454,7 +5436,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5522,7 +5504,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P31">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q31">
         <v>97.5</v>
@@ -5531,7 +5513,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>90.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -5726,7 +5708,7 @@
         <v>93.2</v>
       </c>
       <c r="P34">
-        <v>97.3</v>
+        <v>98.2</v>
       </c>
       <c r="Q34">
         <v>93.8</v>
@@ -5735,7 +5717,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>90.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -5810,19 +5792,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>87.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="G2" s="2">
-        <v>12.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5842,19 +5824,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5865,28 +5847,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>31</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5897,28 +5879,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>31</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5929,10 +5911,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6">
         <v>31</v>
@@ -5950,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5961,10 +5943,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -5982,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6064,7 +6046,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6096,16 +6078,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920031</v>
+        <v>22330051920038</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6119,22 +6101,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920031</v>
+        <v>22330051920191</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6142,162 +6124,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920031</v>
+        <v>22330051920327</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920191</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920191</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920191</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920038</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920189</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920327</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
